--- a/outputs/comparaison_branches/comparaison_branches.xlsx
+++ b/outputs/comparaison_branches/comparaison_branches.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D2" t="n">
         <v>26</v>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" t="n">
         <v>18</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,6 +1179,116 @@
       <c r="D24" t="inlineStr">
         <is>
           <t>detection d un mots similaire à menteur</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>case_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>La cliente s'est montree agressive pendant l'entretien.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressive vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:Z52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6941,6 +7051,430 @@
       <c r="Z48" t="inlineStr">
         <is>
           <t>la personne est une menteuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ideologie_politique</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>regex_iban_fr</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>donnees_personnelles_structurees</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>iban_fr</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8653,6 +9187,332 @@
         </is>
       </c>
       <c r="R24" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{'gliner': 1}</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{'gliner': 1}</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>case_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressive vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>{'gliner': 1}</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>{'regex': 1}</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -8669,7 +9529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10798,6 +11658,202 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10810,7 +11866,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11716,6 +12772,162 @@
       </c>
       <c r="I23" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -11805,7 +13017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17196,6 +18408,500 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ideologie_politique</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressive vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>aucune detection</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>regex_iban_fr</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>donnees_personnelles_structurees</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>iban_fr</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17207,7 +18913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19904,6 +21610,226 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/comparaison_branches/comparaison_branches.xlsx
+++ b/outputs/comparaison_branches/comparaison_branches.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
         <v>26</v>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
         <v>18</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Detection par lemmatisation spaCy de agressive vers agressif sans synonyme configure</t>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
         </is>
       </c>
     </row>
@@ -1289,6 +1289,50 @@
       <c r="D29" t="inlineStr">
         <is>
           <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z52"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7475,6 +7519,218 @@
       <c r="Z52" t="inlineStr">
         <is>
           <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9337,7 +9593,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Detection par lemmatisation spaCy de agressive vers agressif sans synonyme configure</t>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -9513,6 +9769,138 @@
         </is>
       </c>
       <c r="R29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>{'spacy': 1}</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>{'spacy': 1}</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -9529,7 +9917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K47"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11854,6 +12242,104 @@
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11866,7 +12352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12928,6 +13414,84 @@
       </c>
       <c r="I27" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13017,7 +13581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z54"/>
+  <dimension ref="A1:Z56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18641,7 +19205,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detection par lemmatisation spaCy de agressive vers agressif sans synonyme configure</t>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -18902,6 +19466,226 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18913,7 +19697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O52"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21830,6 +22614,116 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/outputs/comparaison_branches/comparaison_branches.xlsx
+++ b/outputs/comparaison_branches/comparaison_branches.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D2" t="n">
         <v>26</v>
@@ -508,7 +508,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D4" t="n">
         <v>18</v>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -580,7 +580,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D8" t="n">
         <v>26</v>
@@ -598,7 +598,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="D9" t="n">
         <v>15</v>
@@ -616,7 +616,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D10" t="n">
         <v>4</v>
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1179,6 +1179,160 @@
       <c r="D24" t="inlineStr">
         <is>
           <t>detection d un mots similaire à menteur</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>case_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>La cliente s'est montree agressive pendant l'entretien.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
         </is>
       </c>
     </row>
@@ -1795,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z48"/>
+  <dimension ref="A1:Z54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6941,6 +7095,642 @@
       <c r="Z48" t="inlineStr">
         <is>
           <t>la personne est une menteuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F49" t="b">
+        <v>0</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>ideologie_politique</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S50" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>regex_iban_fr</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>donnees_personnelles_structurees</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>iban_fr</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="S52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S53" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S54" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
         </is>
       </c>
     </row>
@@ -6981,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R24"/>
+  <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8653,6 +9443,464 @@
         </is>
       </c>
       <c r="R24" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>{'gliner': 1}</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>{'gliner': 1}</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>case_026</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>{'gliner': 1}</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>{'regex': 1}</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>{'spacy': 1}</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>generic | spacy | gliner | regex</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>{'spacy': 1}</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
         <is>
           <t>{}</t>
         </is>
@@ -8669,7 +9917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10798,6 +12046,300 @@
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10810,7 +12352,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11715,6 +13257,240 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" t="n">
         <v>1</v>
       </c>
     </row>
@@ -11805,7 +13581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z49"/>
+  <dimension ref="A1:Z56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17196,6 +18972,720 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>phrase sans contexte extension du cas 19 et 20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F50" t="b">
+        <v>0</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>ideologie_politique</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Test d identification d une malaide non presente dans les mots interdit</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F51" t="b">
+        <v>0</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_026</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>aucune detection</t>
+        </is>
+      </c>
+      <c r="F52" t="b">
+        <v>0</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr"/>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Gliner</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Detection GLiNER d une pathologie absente des mots interdits</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>maladie</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ExpReg</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Detection regex d un IBAN francais sans mot cle generique IBAN</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>regex_iban_fr</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>donnees_personnelles_structurees</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>iban_fr</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>variante du cas 26 avec accent sur montrée</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F55" t="b">
+        <v>0</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Spacy</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Detection par lemmatisation spaCy de agressives vers agressif sans synonyme configure</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="F56" t="b">
+        <v>0</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>jugements_de_valeur_et_commentaires_subjectifs</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17207,7 +19697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O48"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19904,6 +22394,336 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>case_024</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>gliner_ideologie_politique</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>extreme droite</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>case_025</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>diabète de type 2</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Le dossier mentionne un diabète de type 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>case_027</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>gliner</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>gliner_maladie</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>sclerose en plaques</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Le questionnaire signale une sclerose en plaques stabilisee.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>case_028</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>IBAN_FR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>FR76 3000 6000 0112 3456 7890 189</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>regex</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Reference transmise: FR76 3000 6000 0112 3456 7890 189.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>case_029</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>agressive</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>La cliente s'est montrée agressive pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>case_030</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>alerte active</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>spacy</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>mots_interdits_045_agressif</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>agressives</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>lemma</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Les clientes sont agressives pendant l'entretien.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
